--- a/Model/mini/data_my/12_公园词频统计.xlsx
+++ b/Model/mini/data_my/12_公园词频统计.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -473,37 +473,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>徐家汇</t>
+          <t>绿地</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>绿地</t>
+          <t>世纪公园</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>世纪公园</t>
+          <t>中山公园</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中山公园</t>
+          <t>外滩</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -513,61 +513,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>外滩</t>
+          <t>广场</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>广场</t>
+          <t>静安寺</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>静安寺</t>
+          <t>口袋公园</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>口袋公园</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>新天地</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>淮海路</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
